--- a/artfynd/A 25981-2024 artfynd.xlsx
+++ b/artfynd/A 25981-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118255829</v>
+        <v>118253639</v>
       </c>
       <c r="B2" t="n">
         <v>97821</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721850</v>
+        <v>721908</v>
       </c>
       <c r="R2" t="n">
-        <v>6378576</v>
+        <v>6378715</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118255819</v>
+        <v>118255829</v>
       </c>
       <c r="B3" t="n">
-        <v>97763</v>
+        <v>97821</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>219797</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721903</v>
+        <v>721850</v>
       </c>
       <c r="R3" t="n">
-        <v>6378564</v>
+        <v>6378576</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118255353</v>
+        <v>118255819</v>
       </c>
       <c r="B4" t="n">
-        <v>97821</v>
+        <v>97763</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219797</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721843</v>
+        <v>721903</v>
       </c>
       <c r="R4" t="n">
-        <v>6378586</v>
+        <v>6378564</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118253639</v>
+        <v>118253744</v>
       </c>
       <c r="B5" t="n">
         <v>97821</v>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721908</v>
+        <v>721966</v>
       </c>
       <c r="R5" t="n">
-        <v>6378715</v>
+        <v>6378807</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118253744</v>
+        <v>118255353</v>
       </c>
       <c r="B6" t="n">
         <v>97821</v>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721966</v>
+        <v>721843</v>
       </c>
       <c r="R6" t="n">
-        <v>6378807</v>
+        <v>6378586</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 25981-2024 artfynd.xlsx
+++ b/artfynd/A 25981-2024 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>118253358</v>
       </c>
       <c r="B7" t="n">
-        <v>97824</v>
+        <v>97831</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>118255309</v>
       </c>
       <c r="B8" t="n">
-        <v>97824</v>
+        <v>97831</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
